--- a/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
+++ b/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="missing_from_prediction" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="extra_prediction" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="field_accuracy" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,102 +434,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Pubmed PMID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Top SNP</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>OR_nonref</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>#dbSNP_hg38_chr</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dbSNP_hg38_position</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RA 1(Reported Allele 1)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cohort_simple3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Population_map</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sample size</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Analysis group</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Phenotype</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Phenotype-derived</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LocusName</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>nonref_allele</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>nonref_effect</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>nearest_gene_symb</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Study type</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Study Design</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>most_severe_consequence</t>
         </is>
@@ -4373,86 +4386,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>pmid</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snp</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pvalue</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>effect</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>effect_match</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>chr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>bp</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ra1</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cohort</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sample_size</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>analysis_group</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>phenotype</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>phenotype_derived</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>locus_name</t>
         </is>
@@ -4461,7 +4474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4484,21 +4497,19 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -4509,7 +4520,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4532,21 +4543,19 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -4557,7 +4566,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4580,28 +4589,26 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4624,28 +4631,26 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4668,21 +4673,19 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -4693,7 +4696,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4716,21 +4719,19 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -4741,7 +4742,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4764,21 +4765,19 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -4789,7 +4788,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4812,21 +4811,19 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -4837,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4860,21 +4857,19 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -4885,7 +4880,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4908,28 +4903,26 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4952,28 +4945,26 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4996,21 +4987,19 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -5021,7 +5010,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5044,21 +5033,19 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -5069,7 +5056,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5092,21 +5079,19 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -5117,7 +5102,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5140,21 +5125,19 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -5165,7 +5148,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5188,21 +5171,19 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -5213,7 +5194,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5236,21 +5217,19 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -5261,7 +5240,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5284,21 +5263,19 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -5309,7 +5286,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5332,21 +5309,19 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -5357,7 +5332,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5380,21 +5355,19 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -5405,7 +5378,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5428,21 +5401,19 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -5453,7 +5424,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5476,21 +5447,19 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -5501,7 +5470,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5524,21 +5493,19 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -5549,7 +5516,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5572,21 +5539,19 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>adgc;igap</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>74046</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -5597,7 +5562,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5620,21 +5585,19 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>adgc</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -5645,7 +5608,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5668,2345 +5631,23 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>adsp</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>adsp</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CD33</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>rs6733839</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1.51e-07</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.07358</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>rs6733839</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>rs6733839</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2.05e-06</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.08763</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>rs6733839</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1.83e-11</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.1275</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>6.96e-09</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.12075</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1.71e-08</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.12637</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1.53e-17</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.19363</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>GATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>GATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>3.53e-09</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.129</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.878974</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>TRIM4</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>TRIM4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>4.15e-09</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-0.115</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.891366</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1.58e-08</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-0.107</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.898526</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3.77e-08</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.879853</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2.3e-07</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1.15835</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>ZKSCAN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>ZKSCAN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>6.07e-05</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1.08981</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>PVRIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>PVRIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>3.68e-06</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1.11516</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>6.86e-18</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1.12075</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1.18e-17</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.08981</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>7.33e-12</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1.09856</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2.31e-06</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.9323939999999999</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1.07e-07</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.15027</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>8.13e-05</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2.34e-12</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.921272</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>0.00497</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>1.15e-06</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.860708</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1.59e-06</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-0.179</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.836106</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>adgc;adni</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>adgc;adni;igap</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>rs8093731</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1.36e-08</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="F70" t="n">
-        <v>2.15977</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>igap</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>DLGAP1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>rs8093731</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1.11e-05</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="F71" t="n">
-        <v>2.02587</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>igap</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>NETO1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>rs4147929</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>3.94e-06</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1.29563</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>igap</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>EID2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>rs10948363</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1.64e-05</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1.40917</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>igap</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>AK9</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>rs3865444</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1.96e-05</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-0.255</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.774916</v>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>igap</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="n">
-        <v>74046</v>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>IER2</t>
         </is>
       </c>
     </row>
@@ -8021,53 +5662,1846 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pmid</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snp</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pmid</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pvalue</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>effect_match</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>chr</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>bp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ra1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pvalue</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>effect</t>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>sample_size</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_group</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>phenotype</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>phenotype_derived</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>locus_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.07e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.15027</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.15027</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>47536319</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>763</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>mybpc3 (11725151_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CELF1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.15e-06</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.16183</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.16183</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>60156035</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>763</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ms4a4a (11751570_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.59e-06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.19602</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.19602</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>60156035</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>763</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ms4a4a (11732865_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.34e-12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.08546</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.08546</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>60156035</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>763</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ms4a6a (11716846_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rs8093731</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.02587</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.02587</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>31508995</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>nabec</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>85</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>DSG2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rs8093731</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.36e-08</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.15977</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.15977</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>31508995</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>nabec</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>85</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>DSG2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rs4147929</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.94e-06</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.29563</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.29563</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1063444</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ukbec</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>49</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eid2b (t3862068) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ABCA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rs3865444</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.96e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.774916</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.774916</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>51224706</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ukbec</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>49</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ier2 (t3822216) expression in temporal cortex</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>CD33</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.51e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.07251</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.07251</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>127135234</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>763</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>bin1 (11719631_s_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.05e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.08329</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.08329</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>127135234</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>763</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>bin1 (11746895_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rs10948363</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.64e-05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.40917</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.40917</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>47520026</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ukbec</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>49</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ak9 (t2969159) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>CD2AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.3e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.16183</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.16183</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>763</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>zkscan1 (11760665_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6.07e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>763</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>pvrig (11730247_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.53e-17</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.19722</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.19722</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>763</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>gats (11722909_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.58e-08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.11293</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.11293</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>763</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>pilrb (11730023 s at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.53e-09</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.13769</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.13769</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>763</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>trim4 (11736388_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.77e-08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.13655</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.13655</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>763</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>pilrb (11730022_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4.15e-09</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.12187</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.12187</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>763</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>pilrb (11743311_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.68e-06</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.11628</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.11628</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>143413669</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>763</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>loc154761 (11755327 s at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>EPHA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.31e-06</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.07251</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.07251</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>27337604</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>763</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>trim35 (11723344_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>PIK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.18e-17</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>27337604</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>763</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ptk2b (11720982 s at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>PIK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>6.86e-18</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.11628</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.11628</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>27337604</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>763</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ptk2b (11720981_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>PIK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>7.33e-12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>27337604</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>763</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ptk2b (11720980_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>PIK2B</t>
         </is>
       </c>
     </row>
@@ -8082,53 +7516,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pmid</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snp</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pmid</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pvalue</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>effect_match</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>chr</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>bp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ra1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pvalue</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>effect</t>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>sample_size</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_group</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>phenotype</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>phenotype_derived</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>locus_name</t>
         </is>
       </c>
     </row>
@@ -8145,21 +7624,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>rs2296160</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.00856</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.11</v>
+      </c>
       <c r="H2" t="n">
-        <v>0.00856</v>
-      </c>
-      <c r="I2" t="n">
         <v>1.11</v>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8174,20 +7676,47 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>rs9270303</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
       <c r="H3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="I3" t="n">
         <v>1.15</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>HLA-DRB5</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -8203,20 +7732,47 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>rs2405442</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.89</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.00109</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.89</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -8232,21 +7788,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>rs1859788</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.00112</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.89</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.00112</v>
-      </c>
-      <c r="I5" t="n">
         <v>0.89</v>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8261,20 +7840,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>rs7982</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.00162</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.9</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -8290,20 +7896,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>rs2293576</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.07</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.07</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>CELF1</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -8319,20 +7952,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>rs12453</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.89</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.00036</v>
-      </c>
-      <c r="I8" t="n">
         <v>0.89</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -8348,20 +8008,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>rs3752246</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>9.890000000000001e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.18</v>
+      </c>
       <c r="H9" t="n">
-        <v>9.890000000000001e-05</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.18</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ABCA7</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -8377,675 +8064,48 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>rs12459419</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="H10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I10" t="n">
         <v>0.9399999999999999</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rs6733839</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>rs6733839</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>snp_not_in_gold</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>1.83e-11</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>snp_not_in_gold</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>snp_not_in_gold</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>6.96e-09</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.114</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>snp_not_in_gold</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>snp_not_in_gold</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>1.71e-08</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.119</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>snp_not_in_gold</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="n">
-        <v>8.13e-05</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
-        <v>0.00497</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>adsp</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ms4a6a + abca7 + alzheimers disease</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>CD33</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9058,46 +8118,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key_cols</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_pred_rows</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_gold_rows</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>row_precision</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>row_recall</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>row_f1</t>
         </is>
@@ -9106,7 +8166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9135,100 +8195,87 @@
         <v>0.5151515151515152</v>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>metric_set</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>fields</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>easy_fields</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pvalue,effect,cohort,sample_size,analysis_group,population,chr</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4358974358974359</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1214285714285714</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1899441340782123</v>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>all_advp_fields</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>pmid,snp,pvalue</t>
-        </is>
+          <t>pmid,snp,chr,pvalue,effect,cohort,sample_size,analysis_group,population,locus_name,phenotype,phenotype_derived</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4662921348314606</v>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>0.1729166666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.4390243902439024</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pmid,snp,pvalue</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>combined_inputs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pmid,snp,pvalue</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>73</v>
-      </c>
-      <c r="E5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.547945205479452</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.7079646017699115</v>
+        <v>0.2522796352583587</v>
       </c>
     </row>
   </sheetData>

--- a/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
+++ b/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
@@ -4386,7 +4386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4474,7 +4474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4482,17 +4482,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rs6656401</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.49e-07</v>
+        <v>1.51e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.17</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.07358</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4502,25 +4502,29 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4528,18 +4532,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rs4844600</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.22e-07</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -4548,25 +4548,29 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4574,17 +4578,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.24e-08</v>
+        <v>2.05e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.18</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>1.08763</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4594,21 +4598,29 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4616,18 +4628,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.00856</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -4636,21 +4644,29 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4658,17 +4674,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rs9271192</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.000266</v>
+        <v>1.83e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1.11</v>
+        <v>1.1275</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -4678,25 +4694,29 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4704,18 +4724,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rs9270303</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.15</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -4724,25 +4740,29 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4750,17 +4770,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.00141</v>
+        <v>6.96e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>0.92</v>
+        <v>0.114</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>1.12075</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -4770,25 +4790,29 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4796,18 +4820,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.00212</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.92</v>
-      </c>
+        <v>0.68</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -4816,25 +4836,29 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4842,17 +4866,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.00109</v>
+        <v>1.71e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.89</v>
+        <v>0.119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>1.12637</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -4862,25 +4886,29 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4888,18 +4916,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.00562</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.93</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -4908,21 +4932,29 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4930,17 +4962,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.00112</v>
+        <v>1.53e-17</v>
       </c>
       <c r="E12" t="n">
-        <v>0.89</v>
+        <v>0.177</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>1.19363</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4950,21 +4982,29 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>GATS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4972,18 +5012,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rs9331896</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.00102</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.92</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -4992,25 +5028,29 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5018,17 +5058,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.000364</v>
+        <v>3.53e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>0.91</v>
+        <v>-0.129</v>
       </c>
       <c r="F14" t="n">
-        <v>0.91</v>
+        <v>0.878974</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -5038,25 +5078,29 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5064,18 +5108,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.00162</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -5084,25 +5124,29 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5110,17 +5154,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.054</v>
+        <v>4.15e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>1.05</v>
+        <v>-0.115</v>
       </c>
       <c r="F16" t="n">
-        <v>1.05</v>
+        <v>0.891366</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -5130,25 +5174,29 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5156,18 +5204,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.03</v>
-      </c>
+        <v>0.85</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -5176,25 +5220,29 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5202,17 +5250,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.04</v>
+        <v>1.58e-08</v>
       </c>
       <c r="E18" t="n">
-        <v>1.07</v>
+        <v>-0.107</v>
       </c>
       <c r="F18" t="n">
-        <v>1.07</v>
+        <v>0.898526</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -5222,25 +5270,29 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5248,18 +5300,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.22e-09</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.86</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -5268,25 +5316,29 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5294,17 +5346,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.34e-09</v>
+        <v>3.77e-08</v>
       </c>
       <c r="E20" t="n">
-        <v>0.86</v>
+        <v>-0.128</v>
       </c>
       <c r="F20" t="n">
-        <v>0.86</v>
+        <v>0.879853</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -5314,25 +5366,29 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5340,18 +5396,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.00036</v>
-      </c>
-      <c r="E21" t="n">
         <v>0.89</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -5360,25 +5412,29 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5386,17 +5442,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rs4147929</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.00139</v>
+        <v>2.3e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.12</v>
+        <v>0.147</v>
       </c>
       <c r="F22" t="n">
-        <v>1.12</v>
+        <v>1.15835</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -5406,25 +5462,29 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5432,18 +5492,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -5452,25 +5508,29 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5478,17 +5538,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.890000000000001e-05</v>
+        <v>6.07e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>1.18</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18</v>
+        <v>1.08981</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -5498,25 +5558,29 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>PVRIG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5524,18 +5588,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rs3865444</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.000449</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.91</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -5544,25 +5604,29 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>PVRIG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5570,17 +5634,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.000402</v>
+        <v>3.68e-06</v>
       </c>
       <c r="E26" t="n">
-        <v>0.91</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="n">
-        <v>0.91</v>
+        <v>1.11516</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -5590,25 +5654,29 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>LOC154761</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5616,18 +5684,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -5636,18 +5700,790 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6.86e-18</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.12075</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.18e-17</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.08981</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7.33e-12</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.09856</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.31e-06</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9323939999999999</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1.07e-07</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.15027</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>8.13e-05</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.34e-12</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.921272</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1.15e-06</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.860708</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.59e-06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.836106</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -5662,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5774,25 +6610,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs4844600</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.07e-07</v>
+        <v>4.22e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15027</v>
+        <v>1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>1.15027</v>
+        <v>1.17</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>47536319</v>
+        <v>207505962</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -5801,7 +6637,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -5810,7 +6646,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -5819,17 +6655,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mybpc3 (11725151_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
@@ -5850,25 +6686,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs6656401</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.15e-06</v>
+        <v>8.49e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.16183</v>
+        <v>1.17</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16183</v>
+        <v>1.17</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>60156035</v>
+        <v>207518704</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5877,7 +6713,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -5886,7 +6722,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -5895,17 +6731,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ms4a4a (11751570_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
@@ -5926,25 +6762,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59e-06</v>
+        <v>4.24e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.19602</v>
+        <v>1.18</v>
       </c>
       <c r="H4" t="n">
-        <v>1.19602</v>
+        <v>1.18</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>60156035</v>
+        <v>207621975</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5953,7 +6789,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -5962,7 +6798,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -5971,17 +6807,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ms4a4a (11732865_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
@@ -6002,17 +6838,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.34e-12</v>
+        <v>0.24</v>
       </c>
       <c r="G5" t="n">
-        <v>1.08546</v>
+        <v>1.03</v>
       </c>
       <c r="H5" t="n">
-        <v>1.08546</v>
+        <v>1.03</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -6020,7 +6856,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>60156035</v>
+        <v>47413435</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -6029,7 +6865,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -6038,7 +6874,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -6047,17 +6883,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ms4a6a (11716846_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
@@ -6078,25 +6914,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs8093731</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.11e-05</v>
+        <v>0.054</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02587</v>
+        <v>1.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02587</v>
+        <v>1.05</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>31508995</v>
+        <v>47536319</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -6105,7 +6941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>nabec</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -6114,7 +6950,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>85</v>
+        <v>15330</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -6123,17 +6959,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>DSG2</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
@@ -6154,25 +6990,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs8093731</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.36e-08</v>
+        <v>7.22e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.15977</v>
+        <v>0.86</v>
       </c>
       <c r="H7" t="n">
-        <v>2.15977</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>31508995</v>
+        <v>60156035</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -6181,7 +7017,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>nabec</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6190,7 +7026,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>85</v>
+        <v>15330</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -6199,17 +7035,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>DSG2</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6230,25 +7066,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs4147929</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.94e-06</v>
+        <v>1.34e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.29563</v>
+        <v>0.86</v>
       </c>
       <c r="H8" t="n">
-        <v>1.29563</v>
+        <v>0.86</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1063444</v>
+        <v>60178272</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -6257,7 +7093,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ukbec</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -6266,7 +7102,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>49</v>
+        <v>15330</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -6275,17 +7111,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>eid2b (t3862068) expression in frontal cortex</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6306,25 +7142,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs3865444</t>
+          <t>rs8093731</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96e-05</v>
+        <v>1.11e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.774916</v>
+        <v>2.02587</v>
       </c>
       <c r="H9" t="n">
-        <v>0.774916</v>
+        <v>2.02587</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>51224706</v>
+        <v>31508995</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -6333,7 +7169,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ukbec</t>
+          <t>nabec</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -6342,7 +7178,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -6351,7 +7187,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ier2 (t3822216) expression in temporal cortex</t>
+          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -6361,7 +7197,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>DSG2</t>
         </is>
       </c>
     </row>
@@ -6382,25 +7218,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs8093731</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.51e-07</v>
+        <v>1.36e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>1.07251</v>
+        <v>2.15977</v>
       </c>
       <c r="H10" t="n">
-        <v>1.07251</v>
+        <v>2.15977</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>127135234</v>
+        <v>31508995</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -6409,7 +7245,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>nabec</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -6418,7 +7254,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>763</v>
+        <v>85</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -6427,7 +7263,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>bin1 (11719631_s_at) expression in blood</t>
+          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -6437,7 +7273,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>DSG2</t>
         </is>
       </c>
     </row>
@@ -6458,25 +7294,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.05e-06</v>
+        <v>0.0027</v>
       </c>
       <c r="G11" t="n">
-        <v>1.08329</v>
+        <v>1.11</v>
       </c>
       <c r="H11" t="n">
-        <v>1.08329</v>
+        <v>1.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>127135234</v>
+        <v>1056493</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -6485,7 +7321,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -6494,7 +7330,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -6503,17 +7339,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>bin1 (11746895_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -6534,25 +7370,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rs10948363</t>
+          <t>rs4147929</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.64e-05</v>
+        <v>3.94e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>1.40917</v>
+        <v>1.29563</v>
       </c>
       <c r="H12" t="n">
-        <v>1.40917</v>
+        <v>1.29563</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47520026</v>
+        <v>1063444</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -6579,7 +7415,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ak9 (t2969159) expression in frontal cortex</t>
+          <t>eid2b (t3862068) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -6589,7 +7425,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CD2AP</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -6610,25 +7446,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs4147929</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3e-07</v>
+        <v>0.00139</v>
       </c>
       <c r="G13" t="n">
-        <v>1.16183</v>
+        <v>1.12</v>
       </c>
       <c r="H13" t="n">
-        <v>1.16183</v>
+        <v>1.12</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>100406823</v>
+        <v>1063444</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6637,7 +7473,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6646,7 +7482,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -6655,17 +7491,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>zkscan1 (11760665_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -6686,25 +7522,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3865444</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.07e-05</v>
+        <v>1.96e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>1.09417</v>
+        <v>0.774916</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09417</v>
+        <v>0.774916</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>100406823</v>
+        <v>51224706</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6713,7 +7549,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>ukbec</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6722,7 +7558,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>763</v>
+        <v>49</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -6731,7 +7567,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>pvrig (11730247_a_at) expression in blood</t>
+          <t>ier2 (t3822216) expression in temporal cortex</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -6741,7 +7577,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -6762,25 +7598,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3865444</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.53e-17</v>
+        <v>0.000449</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19722</v>
+        <v>0.91</v>
       </c>
       <c r="H15" t="n">
-        <v>1.19722</v>
+        <v>0.91</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>100406823</v>
+        <v>51224706</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -6789,7 +7625,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6798,7 +7634,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -6807,17 +7643,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>gats (11722909_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -6838,25 +7674,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.58e-08</v>
+        <v>0.000402</v>
       </c>
       <c r="G16" t="n">
-        <v>1.11293</v>
+        <v>0.91</v>
       </c>
       <c r="H16" t="n">
-        <v>1.11293</v>
+        <v>0.91</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>100406823</v>
+        <v>51225221</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -6865,7 +7701,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6874,7 +7710,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -6883,17 +7719,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>pilrb (11730023 s at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -6914,25 +7750,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs9271192</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.53e-09</v>
+        <v>0.000266</v>
       </c>
       <c r="G17" t="n">
-        <v>1.13769</v>
+        <v>1.11</v>
       </c>
       <c r="H17" t="n">
-        <v>1.13769</v>
+        <v>1.11</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>100406823</v>
+        <v>32610753</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -6941,7 +7777,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -6950,7 +7786,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -6959,17 +7795,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>trim4 (11736388_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
@@ -6990,25 +7826,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs10948363</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.77e-08</v>
+        <v>1.64e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>1.13655</v>
+        <v>1.40917</v>
       </c>
       <c r="H18" t="n">
-        <v>1.13655</v>
+        <v>1.40917</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>100406823</v>
+        <v>47520026</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -7017,7 +7853,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>ukbec</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7026,7 +7862,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>763</v>
+        <v>49</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -7035,7 +7871,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>pilrb (11730022_a_at) expression in blood</t>
+          <t>ak9 (t2969159) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -7045,7 +7881,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD2AP</t>
         </is>
       </c>
     </row>
@@ -7066,17 +7902,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.15e-09</v>
+        <v>0.00212</v>
       </c>
       <c r="G19" t="n">
-        <v>1.12187</v>
+        <v>0.92</v>
       </c>
       <c r="H19" t="n">
-        <v>1.12187</v>
+        <v>0.92</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7084,7 +7920,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>100406823</v>
+        <v>100373690</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -7093,7 +7929,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -7102,7 +7938,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -7111,12 +7947,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>pilrb (11743311_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -7142,17 +7978,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.68e-06</v>
+        <v>0.00562</v>
       </c>
       <c r="G20" t="n">
-        <v>1.11628</v>
+        <v>0.93</v>
       </c>
       <c r="H20" t="n">
-        <v>1.11628</v>
+        <v>0.93</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7160,7 +7996,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>143413669</v>
+        <v>100374211</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -7169,7 +8005,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -7178,7 +8014,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -7187,17 +8023,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>loc154761 (11755327 s at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>EPHA1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7218,25 +8054,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.31e-06</v>
+        <v>0.00141</v>
       </c>
       <c r="G21" t="n">
-        <v>1.07251</v>
+        <v>0.92</v>
       </c>
       <c r="H21" t="n">
-        <v>1.07251</v>
+        <v>0.92</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>27337604</v>
+        <v>100406823</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -7245,7 +8081,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -7254,7 +8090,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -7263,17 +8099,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>trim35 (11723344_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>PIK2B</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7294,17 +8130,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.18e-17</v>
+        <v>0.000364</v>
       </c>
       <c r="G22" t="n">
-        <v>1.09417</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09417</v>
+        <v>0.91</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -7312,7 +8148,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>27337604</v>
+        <v>27604964</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -7321,7 +8157,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -7330,7 +8166,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -7339,17 +8175,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ptk2b (11720982 s at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>PIK2B</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -7370,17 +8206,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs9331896</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6.86e-18</v>
+        <v>0.00102</v>
       </c>
       <c r="G23" t="n">
-        <v>1.11628</v>
+        <v>0.92</v>
       </c>
       <c r="H23" t="n">
-        <v>1.11628</v>
+        <v>0.92</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -7388,7 +8224,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>27337604</v>
+        <v>27610169</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -7397,7 +8233,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -7406,7 +8242,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -7415,93 +8251,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ptk2b (11720981_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>PIK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>7.33e-12</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.09417</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.09417</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>27337604</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>adni</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>763</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>ptk2b (11720980_a_at) expression in blood</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>PIK2B</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -7516,7 +8276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7624,7 +8384,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -7632,18 +8392,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.00856</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -7652,16 +8408,24 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7671,12 +8435,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -7684,18 +8448,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs9270303</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.15</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -7704,18 +8464,22 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -7727,12 +8491,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -7740,17 +8504,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.00109</v>
+        <v>1.83e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.89</v>
+        <v>0.12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.89</v>
+        <v>1.1275</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -7760,18 +8524,22 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -7783,12 +8551,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -7796,18 +8564,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.00112</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.89</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -7816,16 +8580,24 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7835,12 +8607,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -7848,17 +8620,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.00162</v>
+        <v>6.96e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>0.114</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>1.12075</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -7868,18 +8640,22 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -7891,12 +8667,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -7904,18 +8680,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.07</v>
-      </c>
+        <v>0.68</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -7924,18 +8696,22 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -7947,12 +8723,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -7960,17 +8736,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.00036</v>
+        <v>1.71e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>0.89</v>
+        <v>0.119</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>1.12637</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -7980,18 +8756,22 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8783,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -8016,18 +8796,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9.890000000000001e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.18</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -8036,18 +8812,22 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8844,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8072,18 +8852,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -8092,18 +8868,862 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ms4a6a + abca7 + alzheimers disease</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>GATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>TRIM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>8.13e-05</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -8166,7 +9786,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8180,19 +9800,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="G2" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5151515151515152</v>
+        <v>0.4390243902439024</v>
       </c>
     </row>
   </sheetData>
@@ -8248,13 +9868,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1214285714285714</v>
+        <v>0.06428571428571428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1899441340782123</v>
+        <v>0.0935064935064935</v>
       </c>
     </row>
     <row r="3">
@@ -8269,13 +9889,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4662921348314606</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1729166666666667</v>
+        <v>0.15625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2522796352583587</v>
+        <v>0.1886792452830189</v>
       </c>
     </row>
   </sheetData>

--- a/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
+++ b/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
@@ -4386,7 +4386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4474,7 +4474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4482,17 +4482,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs6656401</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.51e-07</v>
+        <v>8.49e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07099999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.07358</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4502,29 +4502,25 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4532,14 +4528,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs4844600</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>4.22e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.17</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -4548,29 +4548,25 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4578,17 +4574,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.05e-06</v>
+        <v>4.24e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08400000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="F4" t="n">
-        <v>1.08763</v>
+        <v>1.18</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4598,29 +4594,21 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4628,14 +4616,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>0.00856</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.11</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -4644,29 +4636,21 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4674,17 +4658,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs9271192</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.83e-11</v>
+        <v>0.000266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>1.11</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1275</v>
+        <v>1.11</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -4694,29 +4678,25 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4724,14 +4704,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs9270303</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>0.00025</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.15</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -4740,29 +4724,25 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4770,17 +4750,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.96e-09</v>
+        <v>0.00141</v>
       </c>
       <c r="E8" t="n">
-        <v>0.114</v>
+        <v>0.92</v>
       </c>
       <c r="F8" t="n">
-        <v>1.12075</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -4790,29 +4770,25 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4820,14 +4796,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+        <v>0.00212</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -4836,29 +4816,25 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4866,17 +4842,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.71e-08</v>
+        <v>0.00109</v>
       </c>
       <c r="E10" t="n">
-        <v>0.119</v>
+        <v>0.89</v>
       </c>
       <c r="F10" t="n">
-        <v>1.12637</v>
+        <v>0.89</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -4886,29 +4862,25 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4916,14 +4888,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+        <v>0.00562</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.93</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -4932,29 +4908,21 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4962,17 +4930,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.53e-17</v>
+        <v>0.00112</v>
       </c>
       <c r="E12" t="n">
-        <v>0.177</v>
+        <v>0.89</v>
       </c>
       <c r="F12" t="n">
-        <v>1.19363</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4982,29 +4950,21 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>GATS</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5012,14 +4972,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs9331896</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+        <v>0.00102</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -5028,29 +4992,25 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5058,17 +5018,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.53e-09</v>
+        <v>0.000364</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.129</v>
+        <v>0.91</v>
       </c>
       <c r="F14" t="n">
-        <v>0.878974</v>
+        <v>0.91</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -5078,29 +5038,25 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5108,14 +5064,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+        <v>0.00162</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -5124,29 +5084,25 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5154,17 +5110,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.15e-09</v>
+        <v>0.054</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.115</v>
+        <v>1.05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.891366</v>
+        <v>1.05</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -5174,29 +5130,25 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5204,14 +5156,18 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+        <v>0.24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.03</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -5220,29 +5176,25 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5250,17 +5202,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.58e-08</v>
+        <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.107</v>
+        <v>1.07</v>
       </c>
       <c r="F18" t="n">
-        <v>0.898526</v>
+        <v>1.07</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -5270,29 +5222,25 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5300,14 +5248,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+        <v>7.22e-09</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.86</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -5316,29 +5268,25 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5346,17 +5294,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3.77e-08</v>
+        <v>1.34e-09</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.128</v>
+        <v>0.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.879853</v>
+        <v>0.86</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -5366,29 +5314,25 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5396,14 +5340,18 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.89</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.89</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -5412,29 +5360,25 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5442,17 +5386,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs4147929</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.3e-07</v>
+        <v>0.00139</v>
       </c>
       <c r="E22" t="n">
-        <v>0.147</v>
+        <v>1.12</v>
       </c>
       <c r="F22" t="n">
-        <v>1.15835</v>
+        <v>1.12</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -5462,29 +5406,25 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5492,14 +5432,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+        <v>0.0027</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.11</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -5508,29 +5452,25 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5538,17 +5478,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.07e-05</v>
+        <v>9.890000000000001e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08599999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="F24" t="n">
-        <v>1.08981</v>
+        <v>1.18</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -5558,29 +5498,25 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PVRIG</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5588,14 +5524,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3865444</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+        <v>0.000449</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -5604,29 +5544,25 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PVRIG</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5634,17 +5570,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3.68e-06</v>
+        <v>0.000402</v>
       </c>
       <c r="E26" t="n">
-        <v>0.109</v>
+        <v>0.91</v>
       </c>
       <c r="F26" t="n">
-        <v>1.11516</v>
+        <v>0.91</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -5654,29 +5590,25 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>LOC154761</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5684,14 +5616,18 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -5700,790 +5636,18 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>6.86e-18</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.12075</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1.18e-17</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.08981</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>7.33e-12</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.09856</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>2.31e-06</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.9323939999999999</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1.07e-07</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.15027</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>8.13e-05</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2.34e-12</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.921272</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0.00497</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1.15e-06</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.860708</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1.59e-06</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-0.179</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.836106</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -6498,7 +5662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6610,25 +5774,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs4844600</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.22e-07</v>
+        <v>1.07e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.17</v>
+        <v>1.15027</v>
       </c>
       <c r="H2" t="n">
-        <v>1.17</v>
+        <v>1.15027</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>207505962</v>
+        <v>47536319</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -6637,7 +5801,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -6646,7 +5810,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -6655,17 +5819,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>mybpc3 (11725151_at) expression in blood</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
@@ -6686,25 +5850,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs6656401</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.49e-07</v>
+        <v>1.15e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.17</v>
+        <v>1.16183</v>
       </c>
       <c r="H3" t="n">
-        <v>1.17</v>
+        <v>1.16183</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>207518704</v>
+        <v>60156035</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -6713,7 +5877,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -6722,7 +5886,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -6731,17 +5895,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>ms4a4a (11751570_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6762,25 +5926,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.24e-08</v>
+        <v>1.59e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.18</v>
+        <v>1.19602</v>
       </c>
       <c r="H4" t="n">
-        <v>1.18</v>
+        <v>1.19602</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>207621975</v>
+        <v>60156035</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6789,7 +5953,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -6798,7 +5962,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -6807,17 +5971,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>ms4a4a (11732865_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6838,17 +6002,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.24</v>
+        <v>2.34e-12</v>
       </c>
       <c r="G5" t="n">
-        <v>1.03</v>
+        <v>1.08546</v>
       </c>
       <c r="H5" t="n">
-        <v>1.03</v>
+        <v>1.08546</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -6856,7 +6020,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>47413435</v>
+        <v>60156035</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -6865,7 +6029,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -6874,7 +6038,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -6883,17 +6047,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>ms4a6a (11716846_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6914,25 +6078,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs8093731</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.054</v>
+        <v>1.11e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.05</v>
+        <v>2.02587</v>
       </c>
       <c r="H6" t="n">
-        <v>1.05</v>
+        <v>2.02587</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>47536319</v>
+        <v>31508995</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -6941,7 +6105,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>nabec</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -6950,7 +6114,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>15330</v>
+        <v>85</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -6959,17 +6123,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>DSG2</t>
         </is>
       </c>
     </row>
@@ -6990,25 +6154,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs8093731</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7.22e-09</v>
+        <v>1.36e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>0.86</v>
+        <v>2.15977</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>2.15977</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>60156035</v>
+        <v>31508995</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7017,7 +6181,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>nabec</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -7026,7 +6190,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15330</v>
+        <v>85</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -7035,17 +6199,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>DSG2</t>
         </is>
       </c>
     </row>
@@ -7066,25 +6230,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs4147929</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.34e-09</v>
+        <v>3.94e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>0.86</v>
+        <v>1.29563</v>
       </c>
       <c r="H8" t="n">
-        <v>0.86</v>
+        <v>1.29563</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>60178272</v>
+        <v>1063444</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -7093,7 +6257,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ukbec</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7102,7 +6266,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>15330</v>
+        <v>49</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -7111,17 +6275,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>eid2b (t3862068) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -7142,25 +6306,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs8093731</t>
+          <t>rs3865444</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.11e-05</v>
+        <v>1.96e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02587</v>
+        <v>0.774916</v>
       </c>
       <c r="H9" t="n">
-        <v>2.02587</v>
+        <v>0.774916</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>31508995</v>
+        <v>51224706</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7169,7 +6333,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>nabec</t>
+          <t>ukbec</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -7178,7 +6342,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -7187,7 +6351,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
+          <t>ier2 (t3822216) expression in temporal cortex</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -7197,7 +6361,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DSG2</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -7218,25 +6382,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs8093731</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.36e-08</v>
+        <v>1.51e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.15977</v>
+        <v>1.07251</v>
       </c>
       <c r="H10" t="n">
-        <v>2.15977</v>
+        <v>1.07251</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>31508995</v>
+        <v>127135234</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -7245,7 +6409,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>nabec</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -7254,7 +6418,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>85</v>
+        <v>763</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -7263,7 +6427,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
+          <t>bin1 (11719631_s_at) expression in blood</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -7273,7 +6437,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DSG2</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -7294,25 +6458,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.0027</v>
+        <v>2.05e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.11</v>
+        <v>1.08329</v>
       </c>
       <c r="H11" t="n">
-        <v>1.11</v>
+        <v>1.08329</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1056493</v>
+        <v>127135234</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -7321,7 +6485,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -7330,7 +6494,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -7339,17 +6503,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>bin1 (11746895_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -7370,25 +6534,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rs4147929</t>
+          <t>rs10948363</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.94e-06</v>
+        <v>1.64e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>1.29563</v>
+        <v>1.40917</v>
       </c>
       <c r="H12" t="n">
-        <v>1.29563</v>
+        <v>1.40917</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1063444</v>
+        <v>47520026</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -7415,7 +6579,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>eid2b (t3862068) expression in frontal cortex</t>
+          <t>ak9 (t2969159) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -7425,7 +6589,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>CD2AP</t>
         </is>
       </c>
     </row>
@@ -7446,25 +6610,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rs4147929</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.00139</v>
+        <v>2.3e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>1.12</v>
+        <v>1.16183</v>
       </c>
       <c r="H13" t="n">
-        <v>1.12</v>
+        <v>1.16183</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1063444</v>
+        <v>100406823</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -7473,7 +6637,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -7482,7 +6646,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -7491,17 +6655,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>zkscan1 (11760665_at) expression in blood</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7522,25 +6686,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rs3865444</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.96e-05</v>
+        <v>6.07e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.774916</v>
+        <v>1.09417</v>
       </c>
       <c r="H14" t="n">
-        <v>0.774916</v>
+        <v>1.09417</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>51224706</v>
+        <v>100406823</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -7549,7 +6713,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ukbec</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -7558,7 +6722,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -7567,7 +6731,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ier2 (t3822216) expression in temporal cortex</t>
+          <t>pvrig (11730247_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -7577,7 +6741,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7598,25 +6762,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>rs3865444</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.000449</v>
+        <v>1.53e-17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.91</v>
+        <v>1.19722</v>
       </c>
       <c r="H15" t="n">
-        <v>0.91</v>
+        <v>1.19722</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51224706</v>
+        <v>100406823</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -7625,7 +6789,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7634,7 +6798,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -7643,17 +6807,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>gats (11722909_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7674,25 +6838,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.000402</v>
+        <v>1.58e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>0.91</v>
+        <v>1.11293</v>
       </c>
       <c r="H16" t="n">
-        <v>0.91</v>
+        <v>1.11293</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>51225221</v>
+        <v>100406823</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -7701,7 +6865,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7710,7 +6874,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -7719,17 +6883,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>pilrb (11730023 s at) expression in blood</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7750,25 +6914,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rs9271192</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.000266</v>
+        <v>3.53e-09</v>
       </c>
       <c r="G17" t="n">
-        <v>1.11</v>
+        <v>1.13769</v>
       </c>
       <c r="H17" t="n">
-        <v>1.11</v>
+        <v>1.13769</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>32610753</v>
+        <v>100406823</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -7777,7 +6941,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7786,7 +6950,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -7795,17 +6959,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>trim4 (11736388_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7826,25 +6990,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rs10948363</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64e-05</v>
+        <v>3.77e-08</v>
       </c>
       <c r="G18" t="n">
-        <v>1.40917</v>
+        <v>1.13655</v>
       </c>
       <c r="H18" t="n">
-        <v>1.40917</v>
+        <v>1.13655</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47520026</v>
+        <v>100406823</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -7853,7 +7017,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ukbec</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7862,7 +7026,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -7871,7 +7035,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>ak9 (t2969159) expression in frontal cortex</t>
+          <t>pilrb (11730022_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -7881,7 +7045,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>CD2AP</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7066,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.00212</v>
+        <v>4.15e-09</v>
       </c>
       <c r="G19" t="n">
-        <v>0.92</v>
+        <v>1.12187</v>
       </c>
       <c r="H19" t="n">
-        <v>0.92</v>
+        <v>1.12187</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7920,7 +7084,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>100373690</v>
+        <v>100406823</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -7929,7 +7093,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -7938,7 +7102,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -7947,12 +7111,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>pilrb (11743311_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -7978,17 +7142,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.00562</v>
+        <v>3.68e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>0.93</v>
+        <v>1.11628</v>
       </c>
       <c r="H20" t="n">
-        <v>0.93</v>
+        <v>1.11628</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7996,7 +7160,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>100374211</v>
+        <v>143413669</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -8005,7 +7169,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8014,7 +7178,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -8023,17 +7187,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>loc154761 (11755327 s at) expression in blood</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>EPHA1</t>
         </is>
       </c>
     </row>
@@ -8054,25 +7218,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.00141</v>
+        <v>2.31e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>0.92</v>
+        <v>1.07251</v>
       </c>
       <c r="H21" t="n">
-        <v>0.92</v>
+        <v>1.07251</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>100406823</v>
+        <v>27337604</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -8081,7 +7245,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -8090,7 +7254,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -8099,17 +7263,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>trim35 (11723344_at) expression in blood</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>PIK2B</t>
         </is>
       </c>
     </row>
@@ -8130,17 +7294,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.000364</v>
+        <v>1.18e-17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.91</v>
+        <v>1.09417</v>
       </c>
       <c r="H22" t="n">
-        <v>0.91</v>
+        <v>1.09417</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8148,7 +7312,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>27604964</v>
+        <v>27337604</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -8157,7 +7321,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -8166,7 +7330,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -8175,17 +7339,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>ptk2b (11720982 s at) expression in blood</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>PIK2B</t>
         </is>
       </c>
     </row>
@@ -8206,17 +7370,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rs9331896</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.00102</v>
+        <v>6.86e-18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.92</v>
+        <v>1.11628</v>
       </c>
       <c r="H23" t="n">
-        <v>0.92</v>
+        <v>1.11628</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8224,7 +7388,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>27610169</v>
+        <v>27337604</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -8233,7 +7397,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>adni</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -8242,7 +7406,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>15330</v>
+        <v>763</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -8251,17 +7415,93 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>ptk2b (11720981_a_at) expression in blood</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>PIK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>7.33e-12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>27337604</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>adni</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>763</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ptk2b (11720980_a_at) expression in blood</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>PIK2B</t>
         </is>
       </c>
     </row>
@@ -8276,7 +7516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8384,7 +7624,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -8392,14 +7632,18 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>0.00856</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.11</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -8408,24 +7652,16 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8435,12 +7671,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -8448,14 +7684,18 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs9270303</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>0.00025</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.15</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -8464,22 +7704,18 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
@@ -8491,12 +7727,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -8504,17 +7740,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.83e-11</v>
+        <v>0.00109</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.89</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1275</v>
+        <v>0.89</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -8524,22 +7760,18 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -8551,12 +7783,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -8564,14 +7796,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+        <v>0.00112</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.89</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -8580,24 +7816,16 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8607,12 +7835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -8620,17 +7848,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.96e-09</v>
+        <v>0.00162</v>
       </c>
       <c r="G6" t="n">
-        <v>0.114</v>
+        <v>0.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.12075</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -8640,22 +7868,18 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -8667,12 +7891,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -8680,14 +7904,18 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.07</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -8696,22 +7924,18 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
@@ -8723,12 +7947,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -8736,17 +7960,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.71e-08</v>
+        <v>0.00036</v>
       </c>
       <c r="G8" t="n">
-        <v>0.119</v>
+        <v>0.89</v>
       </c>
       <c r="H8" t="n">
-        <v>1.12637</v>
+        <v>0.89</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -8756,22 +7980,18 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -8783,12 +8003,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -8796,14 +8016,18 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+        <v>9.890000000000001e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.18</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -8812,22 +8036,18 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8064,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8852,14 +8072,18 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -8868,862 +8092,18 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>GATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>TRIM4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>ZKSCAN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>PVRIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>8.13e-05</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.00497</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>alzheimers disease + cd33 + amyloid beta peptide + presenilin 2</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -9786,7 +8166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9800,19 +8180,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="G2" t="n">
-        <v>0.45</v>
+        <v>0.425</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.5151515151515152</v>
       </c>
     </row>
   </sheetData>
@@ -9868,13 +8248,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06428571428571428</v>
+        <v>0.1214285714285714</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0935064935064935</v>
+        <v>0.1899441340782123</v>
       </c>
     </row>
     <row r="3">
@@ -9889,13 +8269,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.4662921348314606</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15625</v>
+        <v>0.1729166666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.2522796352583587</v>
       </c>
     </row>
   </sheetData>

--- a/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
+++ b/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
@@ -4386,7 +4386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4474,7 +4474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4482,17 +4482,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rs6656401</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.49e-07</v>
+        <v>1.51e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.17</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.07358</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4502,25 +4502,29 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4528,18 +4532,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rs4844600</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.22e-07</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -4548,25 +4548,29 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4574,17 +4578,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.24e-08</v>
+        <v>2.05e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.18</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>1.08763</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4594,21 +4598,29 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4616,18 +4628,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.00856</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -4636,21 +4644,29 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4658,17 +4674,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rs9271192</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.000266</v>
+        <v>1.83e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1.11</v>
+        <v>1.1275</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -4678,25 +4694,29 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4704,18 +4724,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rs9270303</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.15</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -4724,25 +4740,29 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4750,17 +4770,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.00141</v>
+        <v>6.96e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>0.92</v>
+        <v>0.114</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>1.12075</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -4770,25 +4790,29 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4796,18 +4820,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.00212</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.92</v>
-      </c>
+        <v>0.68</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -4816,25 +4836,29 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4842,17 +4866,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.00109</v>
+        <v>1.71e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.89</v>
+        <v>0.119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>1.12637</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -4862,25 +4886,29 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4888,18 +4916,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.00562</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.93</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -4908,21 +4932,29 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4930,17 +4962,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.00112</v>
+        <v>1.53e-17</v>
       </c>
       <c r="E12" t="n">
-        <v>0.89</v>
+        <v>0.177</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>1.19363</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4950,21 +4982,29 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>GATS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4972,18 +5012,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rs9331896</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.00102</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.92</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -4992,25 +5028,29 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5018,17 +5058,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.000364</v>
+        <v>3.53e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>0.91</v>
+        <v>-0.129</v>
       </c>
       <c r="F14" t="n">
-        <v>0.91</v>
+        <v>0.878974</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -5038,25 +5078,29 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5064,18 +5108,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.00162</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -5084,25 +5124,29 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5110,17 +5154,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.054</v>
+        <v>4.15e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>1.05</v>
+        <v>-0.115</v>
       </c>
       <c r="F16" t="n">
-        <v>1.05</v>
+        <v>0.891366</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -5130,25 +5174,29 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5156,18 +5204,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.03</v>
-      </c>
+        <v>0.85</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -5176,25 +5220,29 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5202,17 +5250,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.04</v>
+        <v>1.58e-08</v>
       </c>
       <c r="E18" t="n">
-        <v>1.07</v>
+        <v>-0.107</v>
       </c>
       <c r="F18" t="n">
-        <v>1.07</v>
+        <v>0.898526</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -5222,25 +5270,29 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5248,18 +5300,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.22e-09</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.86</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -5268,25 +5316,29 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5294,17 +5346,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.34e-09</v>
+        <v>3.77e-08</v>
       </c>
       <c r="E20" t="n">
-        <v>0.86</v>
+        <v>-0.128</v>
       </c>
       <c r="F20" t="n">
-        <v>0.86</v>
+        <v>0.879853</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -5314,25 +5366,29 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5340,18 +5396,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.00036</v>
-      </c>
-      <c r="E21" t="n">
         <v>0.89</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -5360,25 +5412,29 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5386,17 +5442,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rs4147929</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.00139</v>
+        <v>2.3e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.12</v>
+        <v>0.147</v>
       </c>
       <c r="F22" t="n">
-        <v>1.12</v>
+        <v>1.15835</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -5406,25 +5462,29 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5432,18 +5492,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -5452,25 +5508,29 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5478,17 +5538,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.890000000000001e-05</v>
+        <v>6.07e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>1.18</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18</v>
+        <v>1.08981</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -5498,25 +5558,29 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>PVRIG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5524,18 +5588,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rs3865444</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.000449</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.91</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -5544,25 +5604,29 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>PVRIG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5570,17 +5634,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.000402</v>
+        <v>3.68e-06</v>
       </c>
       <c r="E26" t="n">
-        <v>0.91</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="n">
-        <v>0.91</v>
+        <v>1.11516</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -5590,25 +5654,29 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>LOC154761</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5616,18 +5684,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -5636,18 +5700,790 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6.86e-18</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.12075</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.18e-17</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.08981</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7.33e-12</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.09856</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.31e-06</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9323939999999999</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1.07e-07</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.15027</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>8.13e-05</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.34e-12</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.921272</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1.15e-06</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.860708</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.59e-06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.836106</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -5662,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5774,25 +6610,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs4844600</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.07e-07</v>
+        <v>4.22e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15027</v>
+        <v>1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>1.15027</v>
+        <v>1.17</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>47536319</v>
+        <v>207505962</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -5801,7 +6637,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -5810,7 +6646,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -5819,17 +6655,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mybpc3 (11725151_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
@@ -5850,25 +6686,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs6656401</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.15e-06</v>
+        <v>8.49e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.16183</v>
+        <v>1.17</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16183</v>
+        <v>1.17</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>60156035</v>
+        <v>207518704</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5877,7 +6713,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -5886,7 +6722,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -5895,17 +6731,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ms4a4a (11751570_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
@@ -5926,25 +6762,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59e-06</v>
+        <v>4.24e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.19602</v>
+        <v>1.18</v>
       </c>
       <c r="H4" t="n">
-        <v>1.19602</v>
+        <v>1.18</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>60156035</v>
+        <v>207621975</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5953,7 +6789,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -5962,7 +6798,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -5971,17 +6807,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ms4a4a (11732865_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
@@ -6002,17 +6838,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.34e-12</v>
+        <v>0.24</v>
       </c>
       <c r="G5" t="n">
-        <v>1.08546</v>
+        <v>1.03</v>
       </c>
       <c r="H5" t="n">
-        <v>1.08546</v>
+        <v>1.03</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -6020,7 +6856,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>60156035</v>
+        <v>47413435</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -6029,7 +6865,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -6038,7 +6874,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -6047,17 +6883,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ms4a6a (11716846_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
@@ -6078,25 +6914,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs8093731</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.11e-05</v>
+        <v>0.054</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02587</v>
+        <v>1.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02587</v>
+        <v>1.05</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>31508995</v>
+        <v>47536319</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -6105,7 +6941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>nabec</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -6114,7 +6950,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>85</v>
+        <v>15330</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -6123,17 +6959,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>DSG2</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
@@ -6154,25 +6990,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs8093731</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.36e-08</v>
+        <v>7.22e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.15977</v>
+        <v>0.86</v>
       </c>
       <c r="H7" t="n">
-        <v>2.15977</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>31508995</v>
+        <v>60156035</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -6181,7 +7017,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>nabec</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6190,7 +7026,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>85</v>
+        <v>15330</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -6199,17 +7035,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>DSG2</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6230,25 +7066,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs4147929</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.94e-06</v>
+        <v>1.34e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.29563</v>
+        <v>0.86</v>
       </c>
       <c r="H8" t="n">
-        <v>1.29563</v>
+        <v>0.86</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1063444</v>
+        <v>60178272</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -6257,7 +7093,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ukbec</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -6266,7 +7102,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>49</v>
+        <v>15330</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -6275,17 +7111,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>eid2b (t3862068) expression in frontal cortex</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6306,25 +7142,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs3865444</t>
+          <t>rs8093731</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96e-05</v>
+        <v>1.11e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.774916</v>
+        <v>2.02587</v>
       </c>
       <c r="H9" t="n">
-        <v>0.774916</v>
+        <v>2.02587</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>51224706</v>
+        <v>31508995</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -6333,7 +7169,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ukbec</t>
+          <t>nabec</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -6342,7 +7178,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -6351,7 +7187,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ier2 (t3822216) expression in temporal cortex</t>
+          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -6361,7 +7197,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>DSG2</t>
         </is>
       </c>
     </row>
@@ -6382,25 +7218,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs8093731</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.51e-07</v>
+        <v>1.36e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>1.07251</v>
+        <v>2.15977</v>
       </c>
       <c r="H10" t="n">
-        <v>1.07251</v>
+        <v>2.15977</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>127135234</v>
+        <v>31508995</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -6409,7 +7245,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>nabec</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -6418,7 +7254,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>763</v>
+        <v>85</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -6427,7 +7263,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>bin1 (11719631_s_at) expression in blood</t>
+          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -6437,7 +7273,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>DSG2</t>
         </is>
       </c>
     </row>
@@ -6458,25 +7294,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.05e-06</v>
+        <v>0.0027</v>
       </c>
       <c r="G11" t="n">
-        <v>1.08329</v>
+        <v>1.11</v>
       </c>
       <c r="H11" t="n">
-        <v>1.08329</v>
+        <v>1.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>127135234</v>
+        <v>1056493</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -6485,7 +7321,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -6494,7 +7330,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -6503,17 +7339,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>bin1 (11746895_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -6534,25 +7370,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rs10948363</t>
+          <t>rs4147929</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.64e-05</v>
+        <v>3.94e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>1.40917</v>
+        <v>1.29563</v>
       </c>
       <c r="H12" t="n">
-        <v>1.40917</v>
+        <v>1.29563</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47520026</v>
+        <v>1063444</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -6579,7 +7415,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ak9 (t2969159) expression in frontal cortex</t>
+          <t>eid2b (t3862068) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -6589,7 +7425,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CD2AP</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -6610,25 +7446,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs4147929</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3e-07</v>
+        <v>0.00139</v>
       </c>
       <c r="G13" t="n">
-        <v>1.16183</v>
+        <v>1.12</v>
       </c>
       <c r="H13" t="n">
-        <v>1.16183</v>
+        <v>1.12</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>100406823</v>
+        <v>1063444</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6637,7 +7473,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6646,7 +7482,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -6655,17 +7491,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>zkscan1 (11760665_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -6686,25 +7522,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3865444</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.07e-05</v>
+        <v>1.96e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>1.09417</v>
+        <v>0.774916</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09417</v>
+        <v>0.774916</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>100406823</v>
+        <v>51224706</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6713,7 +7549,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>ukbec</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6722,7 +7558,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>763</v>
+        <v>49</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -6731,7 +7567,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>pvrig (11730247_a_at) expression in blood</t>
+          <t>ier2 (t3822216) expression in temporal cortex</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -6741,7 +7577,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -6762,25 +7598,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3865444</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.53e-17</v>
+        <v>0.000449</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19722</v>
+        <v>0.91</v>
       </c>
       <c r="H15" t="n">
-        <v>1.19722</v>
+        <v>0.91</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>100406823</v>
+        <v>51224706</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -6789,7 +7625,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6798,7 +7634,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -6807,17 +7643,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>gats (11722909_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -6838,25 +7674,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.58e-08</v>
+        <v>0.000402</v>
       </c>
       <c r="G16" t="n">
-        <v>1.11293</v>
+        <v>0.91</v>
       </c>
       <c r="H16" t="n">
-        <v>1.11293</v>
+        <v>0.91</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>100406823</v>
+        <v>51225221</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -6865,7 +7701,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6874,7 +7710,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -6883,17 +7719,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>pilrb (11730023 s at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -6914,25 +7750,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs9271192</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.53e-09</v>
+        <v>0.000266</v>
       </c>
       <c r="G17" t="n">
-        <v>1.13769</v>
+        <v>1.11</v>
       </c>
       <c r="H17" t="n">
-        <v>1.13769</v>
+        <v>1.11</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>100406823</v>
+        <v>32610753</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -6941,7 +7777,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -6950,7 +7786,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -6959,17 +7795,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>trim4 (11736388_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
@@ -6990,25 +7826,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs10948363</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.77e-08</v>
+        <v>1.64e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>1.13655</v>
+        <v>1.40917</v>
       </c>
       <c r="H18" t="n">
-        <v>1.13655</v>
+        <v>1.40917</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>100406823</v>
+        <v>47520026</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -7017,7 +7853,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>ukbec</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7026,7 +7862,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>763</v>
+        <v>49</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -7035,7 +7871,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>pilrb (11730022_a_at) expression in blood</t>
+          <t>ak9 (t2969159) expression in frontal cortex</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -7045,7 +7881,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>CD2AP</t>
         </is>
       </c>
     </row>
@@ -7066,17 +7902,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.15e-09</v>
+        <v>0.00212</v>
       </c>
       <c r="G19" t="n">
-        <v>1.12187</v>
+        <v>0.92</v>
       </c>
       <c r="H19" t="n">
-        <v>1.12187</v>
+        <v>0.92</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7084,7 +7920,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>100406823</v>
+        <v>100373690</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -7093,7 +7929,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -7102,7 +7938,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -7111,12 +7947,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>pilrb (11743311_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -7142,17 +7978,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.68e-06</v>
+        <v>0.00562</v>
       </c>
       <c r="G20" t="n">
-        <v>1.11628</v>
+        <v>0.93</v>
       </c>
       <c r="H20" t="n">
-        <v>1.11628</v>
+        <v>0.93</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7160,7 +7996,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>143413669</v>
+        <v>100374211</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -7169,7 +8005,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -7178,7 +8014,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -7187,17 +8023,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>loc154761 (11755327 s at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>EPHA1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7218,25 +8054,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.31e-06</v>
+        <v>0.00141</v>
       </c>
       <c r="G21" t="n">
-        <v>1.07251</v>
+        <v>0.92</v>
       </c>
       <c r="H21" t="n">
-        <v>1.07251</v>
+        <v>0.92</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>27337604</v>
+        <v>100406823</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -7245,7 +8081,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -7254,7 +8090,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -7263,17 +8099,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>trim35 (11723344_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>PIK2B</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -7294,17 +8130,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.18e-17</v>
+        <v>0.000364</v>
       </c>
       <c r="G22" t="n">
-        <v>1.09417</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09417</v>
+        <v>0.91</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -7312,7 +8148,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>27337604</v>
+        <v>27604964</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -7321,7 +8157,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -7330,7 +8166,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -7339,17 +8175,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ptk2b (11720982 s at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>PIK2B</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -7370,17 +8206,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs9331896</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6.86e-18</v>
+        <v>0.00102</v>
       </c>
       <c r="G23" t="n">
-        <v>1.11628</v>
+        <v>0.92</v>
       </c>
       <c r="H23" t="n">
-        <v>1.11628</v>
+        <v>0.92</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -7388,7 +8224,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>27337604</v>
+        <v>27610169</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -7397,7 +8233,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>adni</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -7406,7 +8242,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>763</v>
+        <v>15330</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -7415,93 +8251,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ptk2b (11720981_a_at) expression in blood</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>PIK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>7.33e-12</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.09417</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.09417</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>27337604</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>adni</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>763</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>ptk2b (11720980_a_at) expression in blood</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>PIK2B</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -7516,7 +8276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7624,7 +8384,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -7632,18 +8392,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.00856</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -7652,16 +8408,24 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7671,12 +8435,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -7684,18 +8448,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs9270303</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.15</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -7704,18 +8464,22 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -7727,12 +8491,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -7740,17 +8504,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.00109</v>
+        <v>1.83e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.89</v>
+        <v>0.12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.89</v>
+        <v>1.1275</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -7760,18 +8524,22 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -7783,12 +8551,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -7796,18 +8564,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.00112</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.89</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -7816,16 +8580,24 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7835,12 +8607,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -7848,17 +8620,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.00162</v>
+        <v>6.96e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>0.114</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>1.12075</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -7868,18 +8640,22 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -7891,12 +8667,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -7904,18 +8680,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.07</v>
-      </c>
+        <v>0.68</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -7924,18 +8696,22 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -7947,12 +8723,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -7960,17 +8736,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.00036</v>
+        <v>1.71e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>0.89</v>
+        <v>0.119</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>1.12637</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -7980,18 +8756,22 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8783,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -8016,18 +8796,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9.890000000000001e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.18</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -8036,18 +8812,22 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8844,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8072,18 +8852,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -8092,18 +8868,862 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>alzheimers disease + ad + outcome + trait + ad phenotype + disease</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>GATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>TRIM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>8.13e-05</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -8166,7 +9786,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8180,19 +9800,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="G2" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5151515151515152</v>
+        <v>0.4390243902439024</v>
       </c>
     </row>
   </sheetData>
@@ -8248,13 +9868,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1214285714285714</v>
+        <v>0.06428571428571428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1899441340782123</v>
+        <v>0.0935064935064935</v>
       </c>
     </row>
     <row r="3">
@@ -8269,13 +9889,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4662921348314606</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1729166666666667</v>
+        <v>0.15625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2522796352583587</v>
+        <v>0.1886792452830189</v>
       </c>
     </row>
   </sheetData>

--- a/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
+++ b/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
@@ -4386,7 +4386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4474,7 +4474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4482,17 +4482,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs6656401</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.51e-07</v>
+        <v>8.49e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07099999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.07358</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4502,29 +4502,25 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4532,14 +4528,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs4844600</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>4.22e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.17</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -4548,29 +4548,25 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>CR1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4578,17 +4574,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.05e-06</v>
+        <v>4.24e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08400000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="F4" t="n">
-        <v>1.08763</v>
+        <v>1.18</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4598,29 +4594,21 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4628,14 +4616,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>0.00856</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.11</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -4644,29 +4636,21 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4674,17 +4658,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs9271192</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.83e-11</v>
+        <v>0.000266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>1.11</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1275</v>
+        <v>1.11</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -4694,29 +4678,25 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4724,14 +4704,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs9270303</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>0.00025</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.15</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -4740,29 +4724,25 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4770,17 +4750,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.96e-09</v>
+        <v>0.00141</v>
       </c>
       <c r="E8" t="n">
-        <v>0.114</v>
+        <v>0.92</v>
       </c>
       <c r="F8" t="n">
-        <v>1.12075</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -4790,29 +4770,25 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4820,14 +4796,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+        <v>0.00212</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -4836,29 +4816,25 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4866,17 +4842,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.71e-08</v>
+        <v>0.00109</v>
       </c>
       <c r="E10" t="n">
-        <v>0.119</v>
+        <v>0.89</v>
       </c>
       <c r="F10" t="n">
-        <v>1.12637</v>
+        <v>0.89</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -4886,29 +4862,25 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4916,14 +4888,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+        <v>0.00562</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.93</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -4932,29 +4908,21 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4962,17 +4930,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.53e-17</v>
+        <v>0.00112</v>
       </c>
       <c r="E12" t="n">
-        <v>0.177</v>
+        <v>0.89</v>
       </c>
       <c r="F12" t="n">
-        <v>1.19363</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4982,29 +4950,21 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>GATS</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5012,14 +4972,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs9331896</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+        <v>0.00102</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -5028,29 +4992,25 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5058,17 +5018,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.53e-09</v>
+        <v>0.000364</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.129</v>
+        <v>0.91</v>
       </c>
       <c r="F14" t="n">
-        <v>0.878974</v>
+        <v>0.91</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -5078,29 +5038,25 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5108,14 +5064,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+        <v>0.00162</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -5124,29 +5084,25 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5154,17 +5110,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.15e-09</v>
+        <v>0.054</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.115</v>
+        <v>1.05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.891366</v>
+        <v>1.05</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -5174,29 +5130,25 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5204,14 +5156,18 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+        <v>0.24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.03</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -5220,29 +5176,25 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5250,17 +5202,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.58e-08</v>
+        <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.107</v>
+        <v>1.07</v>
       </c>
       <c r="F18" t="n">
-        <v>0.898526</v>
+        <v>1.07</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -5270,29 +5222,25 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5300,14 +5248,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+        <v>7.22e-09</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.86</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -5316,29 +5268,25 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5346,17 +5294,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3.77e-08</v>
+        <v>1.34e-09</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.128</v>
+        <v>0.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.879853</v>
+        <v>0.86</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -5366,29 +5314,25 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5396,14 +5340,18 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.89</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.89</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -5412,29 +5360,25 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5442,17 +5386,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs4147929</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.3e-07</v>
+        <v>0.00139</v>
       </c>
       <c r="E22" t="n">
-        <v>0.147</v>
+        <v>1.12</v>
       </c>
       <c r="F22" t="n">
-        <v>1.15835</v>
+        <v>1.12</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -5462,29 +5406,25 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5492,14 +5432,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+        <v>0.0027</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.11</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -5508,29 +5452,25 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5538,17 +5478,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.07e-05</v>
+        <v>9.890000000000001e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08599999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="F24" t="n">
-        <v>1.08981</v>
+        <v>1.18</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -5558,29 +5498,25 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PVRIG</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5588,14 +5524,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs3865444</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+        <v>0.000449</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -5604,29 +5544,25 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PVRIG</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5634,17 +5570,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3.68e-06</v>
+        <v>0.000402</v>
       </c>
       <c r="E26" t="n">
-        <v>0.109</v>
+        <v>0.91</v>
       </c>
       <c r="F26" t="n">
-        <v>1.11516</v>
+        <v>0.91</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -5654,29 +5590,25 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adgc</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>LOC154761</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5684,14 +5616,18 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -5700,22 +5636,18 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>LOC154761</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -5730,17 +5662,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6.86e-18</v>
+        <v>1.51e-07</v>
       </c>
       <c r="E28" t="n">
-        <v>0.114</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>1.12075</v>
+        <v>1.07358</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -5755,7 +5687,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5765,7 +5697,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -5780,11 +5712,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -5801,7 +5733,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5811,7 +5743,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -5826,17 +5758,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.18e-17</v>
+        <v>2.05e-06</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>1.08981</v>
+        <v>1.08763</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -5851,7 +5783,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5861,7 +5793,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -5876,11 +5808,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -5897,7 +5829,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5907,7 +5839,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -5922,17 +5854,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.33e-12</v>
+        <v>1.83e-11</v>
       </c>
       <c r="E32" t="n">
-        <v>0.094</v>
+        <v>0.12</v>
       </c>
       <c r="F32" t="n">
-        <v>1.09856</v>
+        <v>1.1275</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -5947,7 +5879,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5957,7 +5889,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -5972,11 +5904,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.47</v>
+        <v>0.91</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -5993,7 +5925,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6003,7 +5935,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -6018,17 +5950,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.31e-06</v>
+        <v>6.96e-09</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9323939999999999</v>
+        <v>1.12075</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -6043,7 +5975,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6053,7 +5985,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>TRIM35</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -6068,11 +6000,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -6089,7 +6021,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -6099,7 +6031,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>TRIM35</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -6114,17 +6046,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.07e-07</v>
+        <v>1.71e-08</v>
       </c>
       <c r="E36" t="n">
-        <v>0.14</v>
+        <v>0.119</v>
       </c>
       <c r="F36" t="n">
-        <v>1.15027</v>
+        <v>1.12637</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -6139,7 +6071,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -6149,7 +6081,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>MYBPC3</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -6164,11 +6096,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.13e-05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -6185,7 +6117,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -6195,7 +6127,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>MYBPC3</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -6210,17 +6142,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.34e-12</v>
+        <v>1.53e-17</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.082</v>
+        <v>0.177</v>
       </c>
       <c r="F38" t="n">
-        <v>0.921272</v>
+        <v>1.19363</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -6235,7 +6167,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6245,7 +6177,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
@@ -6260,11 +6192,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.00497</v>
+        <v>0.53</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -6281,7 +6213,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -6291,7 +6223,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6238,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.15e-06</v>
+        <v>3.53e-09</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.15</v>
+        <v>-0.129</v>
       </c>
       <c r="F40" t="n">
-        <v>0.860708</v>
+        <v>0.878974</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -6331,7 +6263,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -6341,7 +6273,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>MS4A4A</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
@@ -6356,11 +6288,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -6377,7 +6309,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -6387,7 +6319,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>MS4A4A</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
@@ -6402,17 +6334,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.59e-06</v>
+        <v>4.15e-09</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.179</v>
+        <v>-0.115</v>
       </c>
       <c r="F42" t="n">
-        <v>0.836106</v>
+        <v>0.891366</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -6427,7 +6359,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6437,7 +6369,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>MS4A4A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
@@ -6452,11 +6384,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -6473,7 +6405,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6483,7 +6415,1465 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1.58e-08</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.107</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.898526</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3.77e-08</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.879853</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2.3e-07</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.15835</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>6.07e-05</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.08981</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3.68e-06</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.11516</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>6.86e-18</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.12075</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1.18e-17</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.08981</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7.33e-12</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.09856</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2.31e-06</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.9323939999999999</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1.07e-07</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.15027</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>8.13e-05</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2.34e-12</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.921272</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1.15e-06</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.860708</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
           <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1.59e-06</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.836106</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>eqtl association</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>rs8093731</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.36e-08</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.15977</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DLGAP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>rs8093731</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.02587</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>NETO1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>rs4147929</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>3.94e-06</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.29563</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>EID2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>rs10948363</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1.64e-05</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.40917</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>AK9</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>rs3865444</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1.96e-05</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.255</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.774916</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>IER2</t>
         </is>
       </c>
     </row>
@@ -6498,7 +7888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6590,1678 +7980,6 @@
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>locus_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>rs4844600</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>4.22e-07</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>207505962</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>CR1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>rs6656401</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>8.49e-07</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>207518704</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>CR1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>rs2296160</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>4.24e-08</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>207621975</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>CR1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>rs2293576</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>47413435</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>CELF1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>47536319</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>CELF1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>7.22e-09</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>60156035</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>rs12453</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.34e-09</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>60178272</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>rs8093731</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.11e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.02587</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.02587</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>31508995</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>nabec</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>85</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>DSG2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>rs8093731</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.36e-08</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.15977</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.15977</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>31508995</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>nabec</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>85</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>DSG2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>rs3752246</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1056493</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>ABCA7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>rs4147929</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>3.94e-06</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.29563</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.29563</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1063444</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ukbec</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>49</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>eid2b (t3862068) expression in frontal cortex</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>ABCA7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>rs4147929</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.00139</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1063444</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>ABCA7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>rs3865444</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.96e-05</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.774916</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.774916</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>51224706</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>ukbec</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>49</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>ier2 (t3822216) expression in temporal cortex</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>CD33</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>rs3865444</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.000449</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>51224706</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>CD33</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>rs12459419</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.000402</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>51225221</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>CD33</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>rs9271192</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.000266</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>32610753</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>HLA-DRB5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>rs10948363</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1.64e-05</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.40917</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.40917</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>47520026</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>ukbec</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>49</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>ak9 (t2969159) expression in frontal cortex</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>CD2AP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>rs2405442</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.00212</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>100373690</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>ZCWPW1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>rs1859788</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.00562</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>100374211</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>ZCWPW1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.00141</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>100406823</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>ZCWPW1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>rs7982</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.000364</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>27604964</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>CLU</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>gold_unmatched</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>missing_in_prediction</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>rs9331896</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.00102</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>27610169</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>adgc</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>caucasian</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>15330</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -8276,7 +7994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8384,7 +8102,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -8392,14 +8110,18 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs2296160</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>0.00856</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.11</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -8408,24 +8130,16 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8435,12 +8149,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -8448,14 +8162,18 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs9270303</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>0.00025</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.15</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -8464,22 +8182,18 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>HLA-DRB5</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8205,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -8504,17 +8218,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2405442</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.83e-11</v>
+        <v>0.00109</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.89</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1275</v>
+        <v>0.89</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -8524,22 +8238,18 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZCWPW1</t>
         </is>
       </c>
     </row>
@@ -8551,12 +8261,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -8564,14 +8274,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1859788</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+        <v>0.00112</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.89</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -8580,24 +8294,16 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8607,12 +8313,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -8620,17 +8326,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs7982</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.96e-09</v>
+        <v>0.00162</v>
       </c>
       <c r="G6" t="n">
-        <v>0.114</v>
+        <v>0.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.12075</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -8640,22 +8346,18 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -8667,12 +8369,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -8680,14 +8382,18 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs2293576</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.07</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -8696,22 +8402,18 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>CELF1</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -8736,17 +8438,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs12453</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.71e-08</v>
+        <v>0.00036</v>
       </c>
       <c r="G8" t="n">
-        <v>0.119</v>
+        <v>0.89</v>
       </c>
       <c r="H8" t="n">
-        <v>1.12637</v>
+        <v>0.89</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -8756,22 +8458,18 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -8783,12 +8481,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -8796,14 +8494,18 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs3752246</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+        <v>9.890000000000001e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.18</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -8812,22 +8514,18 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ABCA7</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8542,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8852,14 +8550,18 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs12459419</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -8868,22 +8570,18 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>adsp</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
+          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>CD33</t>
         </is>
       </c>
     </row>
@@ -8908,11 +8606,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.95</v>
+        <v>0.28</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -8929,7 +8627,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -8939,7 +8637,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -8964,11 +8662,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -8985,7 +8683,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -8995,7 +8693,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -9007,7 +8705,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9020,14 +8718,18 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+        <v>1.83e-11</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.1275</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -9036,22 +8738,22 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -9063,7 +8765,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9076,11 +8778,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -9097,7 +8799,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -9107,7 +8809,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -9119,7 +8821,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9132,14 +8834,18 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+        <v>6.96e-09</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.12075</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -9148,22 +8854,22 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -9175,7 +8881,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9188,11 +8894,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -9209,7 +8915,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -9219,7 +8925,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>PVRIG</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -9231,7 +8937,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9244,14 +8950,18 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+        <v>1.71e-08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.12637</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -9260,22 +8970,22 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>ad association</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>LOC154761</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -9287,7 +8997,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9300,11 +9010,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -9321,7 +9031,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -9331,7 +9041,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -9356,11 +9066,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -9377,7 +9087,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -9387,7 +9097,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
@@ -9412,11 +9122,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.47</v>
+        <v>0.95</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -9433,7 +9143,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -9443,7 +9153,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
@@ -9468,11 +9178,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -9489,7 +9199,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -9499,7 +9209,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>TRIM35</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
@@ -9524,11 +9234,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8.13e-05</v>
+        <v>0.78</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -9545,7 +9255,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -9555,7 +9265,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>MYBPC3</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
@@ -9580,11 +9290,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.00497</v>
+        <v>0.89</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -9601,7 +9311,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -9611,7 +9321,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
@@ -9636,11 +9346,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -9657,7 +9367,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -9667,7 +9377,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>MS4A4A</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
@@ -9692,11 +9402,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -9713,7 +9423,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>alzheimers disease + synonymous mutations + hippocampal sclerosis of aging + alzheimers disease phenotype + alzheimer disease + rest and stress resistance in ageing and alzheimers disease + amyloid beta peptide + presenilin 2 + ms4a6a snps + cancer + cognitive decline</t>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -9722,6 +9432,510 @@
         </is>
       </c>
       <c r="R25" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>8.13e-05</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>pred_unmatched</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pvalue_mismatch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>ad association</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>
@@ -9738,7 +9952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9786,7 +10000,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9800,19 +10014,115 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5151515151515152</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pmid,snp,pvalue</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>0.45</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>0.4390243902439024</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pmid,snp,pvalue</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>combined_inputs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pmid,snp,pvalue</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>73</v>
+      </c>
+      <c r="E5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7079646017699115</v>
       </c>
     </row>
   </sheetData>
@@ -9868,13 +10178,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.2953367875647668</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06428571428571428</v>
+        <v>0.2035714285714286</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0935064935064935</v>
+        <v>0.241014799154334</v>
       </c>
     </row>
     <row r="3">
@@ -9889,13 +10199,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.3307839388145316</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15625</v>
+        <v>0.3604166666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.3449651046859422</v>
       </c>
     </row>
   </sheetData>

--- a/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
+++ b/eval_reports/pmid_30448613_eval_report_advp_like.xlsx
@@ -4386,7 +4386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4474,7 +4474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4482,17 +4482,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rs6656401</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.49e-07</v>
+        <v>1.51e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.17</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.07358</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4502,25 +4502,29 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4528,18 +4532,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rs4844600</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.22e-07</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -4548,25 +4548,29 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CR1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4574,17 +4578,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.24e-08</v>
+        <v>2.05e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.18</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>1.08763</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4594,21 +4598,29 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4616,18 +4628,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.00856</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -4636,21 +4644,29 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4658,17 +4674,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rs9271192</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.000266</v>
+        <v>1.83e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1.11</v>
+        <v>1.1275</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -4678,25 +4694,29 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4704,18 +4724,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rs9270303</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.15</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -4724,25 +4740,29 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4750,17 +4770,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.00141</v>
+        <v>6.96e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>0.92</v>
+        <v>0.114</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>1.12075</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -4770,25 +4790,29 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4796,18 +4820,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.00212</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.92</v>
-      </c>
+        <v>0.68</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -4816,25 +4836,29 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4842,17 +4866,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.00109</v>
+        <v>1.71e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.89</v>
+        <v>0.119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>1.12637</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -4862,25 +4886,29 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4888,18 +4916,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.00562</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.93</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -4908,21 +4932,29 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4930,17 +4962,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.00112</v>
+        <v>1.53e-17</v>
       </c>
       <c r="E12" t="n">
-        <v>0.89</v>
+        <v>0.177</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>1.19363</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4950,21 +4982,29 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>GATS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4972,18 +5012,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rs9331896</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.00102</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.92</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -4992,25 +5028,29 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5018,17 +5058,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.000364</v>
+        <v>3.53e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>0.91</v>
+        <v>-0.129</v>
       </c>
       <c r="F14" t="n">
-        <v>0.91</v>
+        <v>0.878974</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -5038,25 +5078,29 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5064,18 +5108,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.00162</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -5084,25 +5124,29 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5110,17 +5154,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.054</v>
+        <v>4.15e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>1.05</v>
+        <v>-0.115</v>
       </c>
       <c r="F16" t="n">
-        <v>1.05</v>
+        <v>0.891366</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -5130,25 +5174,29 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5156,18 +5204,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.03</v>
-      </c>
+        <v>0.85</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -5176,25 +5220,29 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5202,17 +5250,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.04</v>
+        <v>1.58e-08</v>
       </c>
       <c r="E18" t="n">
-        <v>1.07</v>
+        <v>-0.107</v>
       </c>
       <c r="F18" t="n">
-        <v>1.07</v>
+        <v>0.898526</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -5222,25 +5270,29 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5248,18 +5300,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.22e-09</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.86</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -5268,25 +5316,29 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5294,17 +5346,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.34e-09</v>
+        <v>3.77e-08</v>
       </c>
       <c r="E20" t="n">
-        <v>0.86</v>
+        <v>-0.128</v>
       </c>
       <c r="F20" t="n">
-        <v>0.86</v>
+        <v>0.879853</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -5314,25 +5366,29 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5340,18 +5396,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.00036</v>
-      </c>
-      <c r="E21" t="n">
         <v>0.89</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -5360,25 +5412,29 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5386,17 +5442,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rs4147929</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.00139</v>
+        <v>2.3e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.12</v>
+        <v>0.147</v>
       </c>
       <c r="F22" t="n">
-        <v>1.12</v>
+        <v>1.15835</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -5406,25 +5462,29 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5432,18 +5492,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -5452,25 +5508,29 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5478,17 +5538,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.890000000000001e-05</v>
+        <v>6.07e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>1.18</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18</v>
+        <v>1.08981</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -5498,25 +5558,29 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>PVRIG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5524,18 +5588,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rs3865444</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.000449</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.91</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -5544,25 +5604,29 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>PVRIG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5570,17 +5634,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.000402</v>
+        <v>3.68e-06</v>
       </c>
       <c r="E26" t="n">
-        <v>0.91</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="n">
-        <v>0.91</v>
+        <v>1.11516</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -5590,25 +5654,29 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>adgc</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>LOC154761</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5616,18 +5684,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -5636,18 +5700,22 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>LOC154761</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5730,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.51e-07</v>
+        <v>6.86e-18</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="F28" t="n">
-        <v>1.07358</v>
+        <v>1.12075</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -5687,7 +5755,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5697,7 +5765,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -5712,11 +5780,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -5733,7 +5801,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5743,7 +5811,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -5758,17 +5826,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.05e-06</v>
+        <v>1.18e-17</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.08763</v>
+        <v>1.08981</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -5783,7 +5851,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5793,7 +5861,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -5808,11 +5876,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -5829,7 +5897,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5839,7 +5907,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -5854,17 +5922,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.83e-11</v>
+        <v>7.33e-12</v>
       </c>
       <c r="E32" t="n">
-        <v>0.12</v>
+        <v>0.094</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1275</v>
+        <v>1.09856</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -5879,7 +5947,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5889,7 +5957,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -5904,11 +5972,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.91</v>
+        <v>0.47</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -5925,7 +5993,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5935,7 +6003,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -5950,17 +6018,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6.96e-09</v>
+        <v>2.31e-06</v>
       </c>
       <c r="E34" t="n">
-        <v>0.114</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1.12075</v>
+        <v>0.9323939999999999</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -5975,7 +6043,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5985,7 +6053,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>TRIM35</t>
         </is>
       </c>
     </row>
@@ -6000,11 +6068,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -6021,7 +6089,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -6031,7 +6099,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>TRIM35</t>
         </is>
       </c>
     </row>
@@ -6046,17 +6114,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.71e-08</v>
+        <v>1.07e-07</v>
       </c>
       <c r="E36" t="n">
-        <v>0.119</v>
+        <v>0.14</v>
       </c>
       <c r="F36" t="n">
-        <v>1.12637</v>
+        <v>1.15027</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -6071,7 +6139,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -6081,7 +6149,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>MYBPC3</t>
         </is>
       </c>
     </row>
@@ -6096,11 +6164,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.9399999999999999</v>
+        <v>8.13e-05</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -6117,7 +6185,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -6127,7 +6195,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>MYBPC3</t>
         </is>
       </c>
     </row>
@@ -6142,17 +6210,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.53e-17</v>
+        <v>2.34e-12</v>
       </c>
       <c r="E38" t="n">
-        <v>0.177</v>
+        <v>-0.082</v>
       </c>
       <c r="F38" t="n">
-        <v>1.19363</v>
+        <v>0.921272</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -6167,7 +6235,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6177,7 +6245,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6192,11 +6260,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.53</v>
+        <v>0.00497</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -6213,7 +6281,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -6223,7 +6291,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -6238,17 +6306,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.53e-09</v>
+        <v>1.15e-06</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.129</v>
+        <v>-0.15</v>
       </c>
       <c r="F40" t="n">
-        <v>0.878974</v>
+        <v>0.860708</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -6263,7 +6331,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -6273,7 +6341,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -6288,11 +6356,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -6309,7 +6377,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -6319,7 +6387,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -6334,17 +6402,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.15e-09</v>
+        <v>1.59e-06</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.115</v>
+        <v>-0.179</v>
       </c>
       <c r="F42" t="n">
-        <v>0.891366</v>
+        <v>0.836106</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -6359,7 +6427,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6369,7 +6437,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -6384,11 +6452,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -6405,7 +6473,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6415,1465 +6483,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1.58e-08</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-0.107</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.898526</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3.77e-08</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.879853</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>PILRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2.3e-07</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1.15835</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>ZKSCAN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>ZKSCAN1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>6.07e-05</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1.08981</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>PVRIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>PVRIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>3.68e-06</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1.11516</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>6.86e-18</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1.12075</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1.18e-17</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.08981</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>7.33e-12</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1.09856</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2.31e-06</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.9323939999999999</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1.07e-07</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.15027</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>8.13e-05</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2.34e-12</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.921272</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>0.00497</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>1.15e-06</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.860708</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
           <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1.59e-06</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-0.179</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.836106</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>eqtl association</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>rs8093731</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1.36e-08</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="F70" t="n">
-        <v>2.15977</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>DLGAP1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>rs8093731</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1.11e-05</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="F71" t="n">
-        <v>2.02587</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>NETO1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>rs4147929</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>3.94e-06</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1.29563</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>EID2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>rs10948363</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1.64e-05</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1.40917</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>AK9</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>rs3865444</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1.96e-05</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-0.255</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.774916</v>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>tmem106b + cognitive decline + synonymous mutations + kcnmb2 + hippocampal sclerosis of aging + amyloid beta peptide + alzheimers disease phenotype + rest and stress + alzheimers risk-altering polymorphism + alzheimer disease + alzheimers disease + dna repair + abcc9 + presenilin 2 + clusterin + grn</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>IER2</t>
         </is>
       </c>
     </row>
@@ -7888,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7980,6 +6590,1678 @@
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>locus_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rs4844600</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>4.22e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>207505962</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rs6656401</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>8.49e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>207518704</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>CR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rs2296160</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4.24e-08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>207621975</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>CR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rs2293576</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>47413435</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CELF1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>47536319</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>CELF1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7.22e-09</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>60156035</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rs12453</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.34e-09</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>60178272</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rs8093731</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.02587</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.02587</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>31508995</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>nabec</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>85</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>neto1 (ilmn_1783168) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DSG2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rs8093731</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.36e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.15977</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.15977</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>31508995</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>nabec</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>85</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>dlgap1 (ilmn_2380779) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>DSG2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rs3752246</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1056493</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ABCA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rs4147929</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3.94e-06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.29563</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.29563</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1063444</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ukbec</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>49</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eid2b (t3862068) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ABCA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rs4147929</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1063444</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ABCA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>rs3865444</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.96e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.774916</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.774916</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>51224706</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ukbec</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>49</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ier2 (t3822216) expression in temporal cortex</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>CD33</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>rs3865444</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.000449</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>51224706</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>CD33</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rs12459419</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.000402</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>51225221</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>CD33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>rs9271192</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.000266</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>32610753</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>HLA-DRB5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>rs10948363</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.64e-05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.40917</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.40917</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>47520026</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ukbec</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>49</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ak9 (t2969159) expression in frontal cortex</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>CD2AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>rs2405442</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.00212</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>100373690</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>rs1859788</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.00562</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>100374211</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>100406823</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rs7982</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.000364</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>27604964</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gold_unmatched</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>missing_in_prediction</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>30448613</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>rs9331896</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.00102</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>27610169</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>adgc</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>caucasian</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>15330</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>CLU</t>
         </is>
       </c>
     </row>
@@ -7994,7 +8276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8102,7 +8384,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -8110,18 +8392,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rs2296160</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.00856</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.11</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -8130,16 +8408,24 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8149,12 +8435,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -8162,18 +8448,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rs9270303</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.15</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -8182,18 +8464,22 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HLA-DRB5</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8491,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -8218,17 +8504,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>rs2405442</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.00109</v>
+        <v>1.83e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.89</v>
+        <v>0.12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.89</v>
+        <v>1.1275</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -8238,18 +8524,22 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ZCWPW1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8261,12 +8551,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -8274,18 +8564,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rs1859788</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.00112</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.89</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -8294,16 +8580,24 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8313,12 +8607,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -8326,17 +8620,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rs7982</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.00162</v>
+        <v>6.96e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>0.114</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>1.12075</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -8346,18 +8640,22 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8667,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -8382,18 +8680,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rs2293576</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.07</v>
-      </c>
+        <v>0.68</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -8402,18 +8696,22 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8425,12 +8723,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -8438,17 +8736,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rs12453</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.00036</v>
+        <v>1.71e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>0.89</v>
+        <v>0.119</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>1.12637</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -8458,18 +8756,22 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>eqtl association</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8481,12 +8783,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pvalue_mismatch</t>
+          <t>snp_not_in_gold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -8494,18 +8796,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rs3752246</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9.890000000000001e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.18</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -8514,18 +8812,22 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ABCA7</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8844,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8550,18 +8852,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rs12459419</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -8570,18 +8868,22 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>adsp</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>synonymous mutations + cognitive decline + clusterin + tmem106b + amyloid beta peptide + presenilin 2 + alzheimers disease phenotype + alzheimer disease + rest and stress + alzheimers disease + dna repair + grn + alzheimers risk-altering polymorphism + kcnmb2 + abcc9 + hippocampal sclerosis of aging</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>CD33</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
@@ -8606,11 +8908,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.28</v>
+        <v>0.95</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -8627,7 +8929,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -8637,7 +8939,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
@@ -8662,11 +8964,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rs6733839</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -8683,7 +8985,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -8693,7 +8995,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
@@ -8705,7 +9007,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8718,18 +9020,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.83e-11</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.1275</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -8738,22 +9036,22 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
@@ -8765,7 +9063,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8778,11 +9076,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -8799,7 +9097,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -8809,7 +9107,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
@@ -8821,7 +9119,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8834,18 +9132,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.96e-09</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.12075</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -8854,22 +9148,22 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
     </row>
@@ -8881,7 +9175,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8894,11 +9188,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -8915,7 +9209,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -8925,7 +9219,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>PVRIG</t>
         </is>
       </c>
     </row>
@@ -8937,7 +9231,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8950,18 +9244,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs11771145</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.71e-08</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.12637</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -8970,22 +9260,22 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>eqtl association</t>
+          <t>ad association</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>expression</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>LOC154761</t>
         </is>
       </c>
     </row>
@@ -8997,7 +9287,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>snp_not_in_gold</t>
+          <t>pvalue_mismatch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9010,11 +9300,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -9031,7 +9321,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -9041,7 +9331,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -9066,11 +9356,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.53</v>
+        <v>0.91</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -9087,7 +9377,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -9097,7 +9387,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -9122,11 +9412,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.95</v>
+        <v>0.47</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -9143,7 +9433,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -9153,7 +9443,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>PTK2B</t>
         </is>
       </c>
     </row>
@@ -9178,11 +9468,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -9199,7 +9489,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -9209,7 +9499,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>TRIM35</t>
         </is>
       </c>
     </row>
@@ -9234,11 +9524,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs10838725</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.78</v>
+        <v>8.13e-05</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -9255,7 +9545,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -9265,7 +9555,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MYBPC3</t>
         </is>
       </c>
     </row>
@@ -9290,11 +9580,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.89</v>
+        <v>0.00497</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -9311,7 +9601,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -9321,7 +9611,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>MS4A6A</t>
         </is>
       </c>
     </row>
@@ -9346,11 +9636,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -9367,7 +9657,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -9377,7 +9667,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>
@@ -9402,11 +9692,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -9423,7 +9713,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
+          <t>presenilin 2 + alzheimers disease + hippocampal sclerosis of aging + amyloid beta peptide + ms4a6a snps + rest and stress resistance in ageing and alzheimers disease + cognitive decline + synonymous mutations + alzheimer disease + alzheimers disease phenotype + cancer</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -9432,510 +9722,6 @@
         </is>
       </c>
       <c r="R25" t="inlineStr">
-        <is>
-          <t>PVRIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>TRIM35</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>8.13e-05</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.00497</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>pred_unmatched</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>pvalue_mismatch</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>30448613</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>ad association</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>kcnmb2 + rest and stress + cognitive decline + abcc9 + dna repair + alzheimers disease + clusterin + grn + presenilin 2 + synonymous mutations + alzheimers disease phenotype + alzheimer disease + amyloid beta peptide + tmem106b + hippocampal sclerosis of aging + alzheimers risk-altering polymorphism</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>
@@ -9952,7 +9738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10000,7 +9786,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table1_v1.xlsx</t>
+          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10014,115 +9800,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="G2" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5151515151515152</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table2_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>pmid,snp,pvalue</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>42</v>
-      </c>
-      <c r="E3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H3" t="n">
         <v>0.4390243902439024</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>/Users/justpqa/advp_curator/harmonized_tables_advp/from_30448613_table3_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pmid,snp,pvalue</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>combined_inputs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pmid,snp,pvalue</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>73</v>
-      </c>
-      <c r="E5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.547945205479452</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.7079646017699115</v>
       </c>
     </row>
   </sheetData>
@@ -10178,13 +9868,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2953367875647668</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2035714285714286</v>
+        <v>0.06428571428571428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.241014799154334</v>
+        <v>0.0935064935064935</v>
       </c>
     </row>
     <row r="3">
@@ -10199,13 +9889,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3307839388145316</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3604166666666667</v>
+        <v>0.15625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3449651046859422</v>
+        <v>0.1886792452830189</v>
       </c>
     </row>
   </sheetData>
